--- a/Casos de Testes.xlsx
+++ b/Casos de Testes.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="94">
   <si>
     <t>Feature</t>
   </si>
@@ -371,14 +371,18 @@
   <si>
     <t>Alternativos</t>
   </si>
+  <si>
+    <t>Testes executados antes do tempo previsto sem falhas detectadas
+Detectado uma possível melhoria na especificação referente ao caso de teste de CEP válido com hífen (CT002)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="ddd"/>
-    <numFmt numFmtId="166" formatCode="d"/>
+    <numFmt numFmtId="164" formatCode="ddd"/>
+    <numFmt numFmtId="165" formatCode="d"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -710,12 +714,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -728,47 +726,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -811,10 +773,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -856,6 +818,48 @@
     <xf numFmtId="3" fontId="7" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
@@ -883,597 +887,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="103"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="3"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1680" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="0" baseline="0">
-                <a:gradFill>
-                  <a:gsLst>
-                    <a:gs pos="0">
-                      <a:schemeClr val="dk1">
-                        <a:lumMod val="50000"/>
-                        <a:lumOff val="50000"/>
-                      </a:schemeClr>
-                    </a:gs>
-                    <a:gs pos="100000">
-                      <a:schemeClr val="dk1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                      </a:schemeClr>
-                    </a:gs>
-                  </a:gsLst>
-                  <a:lin ang="5400000" scaled="0"/>
-                </a:gradFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-GB"/>
-              <a:t>Test Cases Burndown</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1680" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="0" baseline="0">
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="85000"/>
-                      <a:lumOff val="15000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Burndown!$E$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Planejado</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:tint val="65000"/>
-                  <a:shade val="95000"/>
-                  <a:satMod val="105000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="17"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="bg1">
-                        <a:lumMod val="50000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="pt-BR"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="dk1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>[1]BurnDown!$A$5:$A$14</c:f>
-              <c:strCache>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>*</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>02/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>03/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>04/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>05/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>08/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>09/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>10/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>11/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>12/04/2024</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Burndown!$E$5:$E$7</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6EA5-48C5-98B9-49AC27037B48}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Burndown!$H$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Fechados</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:shade val="65000"/>
-                  <a:shade val="95000"/>
-                  <a:satMod val="105000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="17"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx2"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="pt-BR"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="dk1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>[1]BurnDown!$A$5:$A$14</c:f>
-              <c:strCache>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>*</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>02/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>03/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>04/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>05/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>08/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>09/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>10/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>11/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>12/04/2024</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Burndown!$H$5:$H$7</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-6EA5-48C5-98B9-49AC27037B48}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="1001836672"/>
-        <c:axId val="581656512"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1001836672"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="dk1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="581656512"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="0"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="581656512"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1001836672"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:legendEntry>
-        <c:idx val="0"/>
-        <c:txPr>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-      </c:legendEntry>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="lt1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr sz="1400"/>
-      </a:pPr>
-      <a:endParaRPr lang="pt-BR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -1701,7 +1114,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.61441818029718398"/>
+          <c:y val="0.36558100832180229"/>
+          <c:w val="0.36566150097771649"/>
+          <c:h val="0.53010118694383412"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:solidFill>
@@ -1720,7 +1142,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr rtl="0">
-            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1">
                   <a:lumMod val="75000"/>
@@ -1796,7 +1218,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -2149,7 +1571,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -2356,9 +1778,9 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.62868607333174265"/>
-          <c:y val="0.30089649916104177"/>
-          <c:w val="0.34101089636522708"/>
+          <c:x val="0.57201942257217853"/>
+          <c:y val="0.3008962821954948"/>
+          <c:w val="0.42434435695538059"/>
           <c:h val="0.6411558948082654"/>
         </c:manualLayout>
       </c:layout>
@@ -2444,6 +1866,555 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="1200"/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="103"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="3"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1680" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="0" baseline="0">
+                <a:gradFill>
+                  <a:gsLst>
+                    <a:gs pos="0">
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                    <a:gs pos="100000">
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="85000"/>
+                        <a:lumOff val="15000"/>
+                      </a:schemeClr>
+                    </a:gs>
+                  </a:gsLst>
+                  <a:lin ang="5400000" scaled="0"/>
+                </a:gradFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Test Cases Burndown</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1680" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="0" baseline="0">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="85000"/>
+                      <a:lumOff val="15000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Burndown!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Planejado</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:tint val="65000"/>
+                  <a:shade val="95000"/>
+                  <a:satMod val="105000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="17"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1">
+                        <a:lumMod val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Burndown!$A$5:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>*</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12/03/2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13/03/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Burndown!$E$5:$E$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6EA5-48C5-98B9-49AC27037B48}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Burndown!$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Fechados</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:shade val="65000"/>
+                  <a:shade val="95000"/>
+                  <a:satMod val="105000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="17"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Burndown!$A$5:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>*</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12/03/2026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13/03/2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Burndown!$H$5:$H$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6EA5-48C5-98B9-49AC27037B48}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="581648352"/>
+        <c:axId val="581655424"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="581648352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="581655424"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="581655424"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="581648352"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="0"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1400"/>
       </a:pPr>
       <a:endParaRPr lang="pt-BR"/>
     </a:p>
@@ -2651,38 +2622,17 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>[1]BurnDown!$A$5:$A$14</c:f>
+              <c:f>Burndown!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>*</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>02/04/2024</c:v>
+                  <c:v>12/03/2026</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>03/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>04/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>05/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>08/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>09/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>10/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>11/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>12/04/2024</c:v>
+                  <c:v>13/03/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2807,38 +2757,17 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>[1]BurnDown!$A$5:$A$14</c:f>
+              <c:f>Burndown!$A$5:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>*</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>02/04/2024</c:v>
+                  <c:v>12/03/2026</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>03/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>04/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>05/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>08/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>09/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>10/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>11/04/2024</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>12/04/2024</c:v>
+                  <c:v>13/03/2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2879,11 +2808,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1001827968"/>
-        <c:axId val="1001828512"/>
+        <c:axId val="863001808"/>
+        <c:axId val="863006160"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1001827968"/>
+        <c:axId val="863001808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2926,7 +2855,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1001828512"/>
+        <c:crossAx val="863006160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="0"/>
         <c:lblAlgn val="ctr"/>
@@ -2934,7 +2863,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1001828512"/>
+        <c:axId val="863006160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2944,7 +2873,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1001827968"/>
+        <c:crossAx val="863001808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3048,8 +2977,42 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -3134,42 +3097,8 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="21">
   <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -3180,6 +3109,1809 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="234">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3689,1809 +5421,6 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-          <a:gs pos="39000">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="lt1">
-              <a:lumMod val="75000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="pct75">
-        <a:fgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:bgClr>
-      </a:pattFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="pct75">
-        <a:fgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:bgClr>
-      </a:pattFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="20000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="20000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="31750" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:alpha val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="50000"/>
-          <a:lumOff val="50000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1">
-          <a:lumMod val="95000"/>
-          <a:alpha val="39000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-          <a:gs pos="39000">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="lt1">
-              <a:lumMod val="75000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="pct75">
-        <a:fgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:bgClr>
-      </a:pattFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="pct75">
-        <a:fgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:bgClr>
-      </a:pattFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="20000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="20000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="31750" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:alpha val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="50000"/>
-          <a:lumOff val="50000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1">
-          <a:lumMod val="95000"/>
-          <a:alpha val="39000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
-  </cs:categoryAxis>
-  <cs:chartArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-          <a:gs pos="39000">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="lt1">
-              <a:lumMod val="75000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="pct75">
-        <a:fgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:bgClr>
-      </a:pattFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="pct75">
-        <a:fgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:bgClr>
-      </a:pattFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="20000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="20000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="31750" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:alpha val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="50000"/>
-          <a:lumOff val="50000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1">
-          <a:lumMod val="95000"/>
-          <a:alpha val="39000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="234">
   <cs:axisTitle>
@@ -6006,23 +5935,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>7621</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Gráfico 4">
+        <xdr:cNvPr id="7" name="Gráfico 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E4B46AC4-349A-4294-A213-4A98991A2618}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D765E148-5685-479E-B43E-BE2BA8056A80}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6046,21 +5975,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>7621</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>403860</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>655320</xdr:colOff>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Gráfico 6">
+        <xdr:cNvPr id="8" name="Gráfico 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D765E148-5685-479E-B43E-BE2BA8056A80}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D765E148-5685-479E-B43E-BE2BA8056A80}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6075,44 +6004,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>7621</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>655320</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Gráfico 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D765E148-5685-479E-B43E-BE2BA8056A80}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6136,7 +6027,45 @@
         <xdr:cNvPr id="10" name="Gráfico 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D765E148-5685-479E-B43E-BE2BA8056A80}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D765E148-5685-479E-B43E-BE2BA8056A80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1097280</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4B46AC4-349A-4294-A213-4A98991A2618}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6174,7 +6103,7 @@
         <xdr:cNvPr id="2" name="CaixaDeTexto 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{34125726-407E-43FC-8D89-A5FEB7DB439C}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34125726-407E-43FC-8D89-A5FEB7DB439C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6220,21 +6149,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>441960</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Gráfico 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E4B46AC4-349A-4294-A213-4A98991A2618}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4B46AC4-349A-4294-A213-4A98991A2618}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6269,178 +6198,56 @@
       <sheetName val="Bugs Cancelados"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="55">
-          <cell r="B55" t="str">
-            <v>Design</v>
-          </cell>
-          <cell r="D55">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="B56" t="str">
-            <v>Not Released</v>
-          </cell>
-          <cell r="D56">
-            <v>1.7857142857142856E-2</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="B57" t="str">
-            <v>Not Executed</v>
-          </cell>
-          <cell r="D57">
-            <v>7.1428571428571425E-2</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="B58" t="str">
-            <v>Closed</v>
-          </cell>
-          <cell r="D58">
-            <v>0.8928571428571429</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="B59" t="str">
-            <v>Failed</v>
-          </cell>
-          <cell r="D59">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="B60" t="str">
-            <v>Blocked</v>
-          </cell>
-          <cell r="D60">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="B61" t="str">
-            <v>Deprioritized/Canceled</v>
-          </cell>
-          <cell r="D61">
-            <v>1.7857142857142856E-2</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
-        <row r="4">
-          <cell r="E4" t="str">
-            <v>Planejado</v>
-          </cell>
-          <cell r="H4" t="str">
-            <v>Fechados</v>
-          </cell>
-        </row>
         <row r="5">
           <cell r="A5" t="str">
             <v>*</v>
-          </cell>
-          <cell r="E5">
-            <v>56</v>
-          </cell>
-          <cell r="H5">
-            <v>56</v>
           </cell>
         </row>
         <row r="6">
           <cell r="A6">
             <v>45384</v>
           </cell>
-          <cell r="E6">
-            <v>51</v>
-          </cell>
-          <cell r="H6">
-            <v>50</v>
-          </cell>
         </row>
         <row r="7">
           <cell r="A7">
             <v>45385</v>
-          </cell>
-          <cell r="E7">
-            <v>46</v>
-          </cell>
-          <cell r="H7">
-            <v>49</v>
           </cell>
         </row>
         <row r="8">
           <cell r="A8">
             <v>45386</v>
           </cell>
-          <cell r="E8">
-            <v>40</v>
-          </cell>
-          <cell r="H8">
-            <v>44</v>
-          </cell>
         </row>
         <row r="9">
           <cell r="A9">
             <v>45387</v>
-          </cell>
-          <cell r="E9">
-            <v>32</v>
-          </cell>
-          <cell r="H9">
-            <v>31</v>
           </cell>
         </row>
         <row r="10">
           <cell r="A10">
             <v>45390</v>
           </cell>
-          <cell r="E10">
-            <v>26</v>
-          </cell>
-          <cell r="H10">
-            <v>23</v>
-          </cell>
         </row>
         <row r="11">
           <cell r="A11">
             <v>45391</v>
-          </cell>
-          <cell r="E11">
-            <v>19</v>
-          </cell>
-          <cell r="H11">
-            <v>16</v>
           </cell>
         </row>
         <row r="12">
           <cell r="A12">
             <v>45392</v>
           </cell>
-          <cell r="E12">
-            <v>11</v>
-          </cell>
-          <cell r="H12">
-            <v>15</v>
-          </cell>
         </row>
         <row r="13">
           <cell r="A13">
             <v>45393</v>
           </cell>
-          <cell r="E13">
-            <v>8</v>
-          </cell>
-          <cell r="H13">
-            <v>5</v>
-          </cell>
         </row>
         <row r="14">
           <cell r="A14">
             <v>45394</v>
-          </cell>
-          <cell r="E14">
-            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -7046,19 +6853,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
     </row>
     <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
@@ -7121,10 +6928,10 @@
       <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="12"/>
+      <c r="B6" s="49"/>
       <c r="C6" s="10" t="s">
         <v>48</v>
       </c>
@@ -7154,242 +6961,244 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="13">
+      <c r="B7" s="51"/>
+      <c r="C7" s="11">
         <v>7</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="11">
         <v>7</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="11">
         <v>0</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="12">
         <f>IFERROR(D7/(C7-E7),0)</f>
         <v>1</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="11">
         <f>COUNTIFS('[1]Bugs IT'!E:E,#REF!)+COUNTIFS('[1]Bugs UAT'!D:D,#REF!)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="12">
         <f>IF(C7=0,0,G7/C7)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="13">
         <v>46093</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="13">
         <v>46093</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="14" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="52" t="s">
         <v>58</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="11" t="s">
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
     </row>
     <row r="10" spans="1:11" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="23">
+      <c r="A10" s="53"/>
+      <c r="B10" s="16">
         <v>46093</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="29"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="47"/>
     </row>
     <row r="27" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
     </row>
     <row r="28" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="49" t="s">
+      <c r="A28" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="50" t="s">
+      <c r="B28" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="51" t="s">
+      <c r="C28" s="37" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="52" t="s">
+      <c r="A29" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="53">
+      <c r="B29" s="39">
         <v>0</v>
       </c>
-      <c r="C29" s="54">
+      <c r="C29" s="40">
         <f>IF(B29=0,0,B29/$B$33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="52" t="s">
+      <c r="A30" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="53">
+      <c r="B30" s="39">
         <v>7</v>
       </c>
-      <c r="C30" s="54">
+      <c r="C30" s="40">
         <f>IF(B30=0,0,B30/$B$33)</f>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="52" t="s">
+      <c r="A31" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="B31" s="53">
+      <c r="B31" s="39">
         <v>0</v>
       </c>
-      <c r="C31" s="54">
+      <c r="C31" s="40">
         <f>IF(B31=0,0,B31/$B$33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="52" t="s">
+      <c r="A32" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="B32" s="53">
+      <c r="B32" s="39">
         <v>0</v>
       </c>
-      <c r="C32" s="54">
+      <c r="C32" s="40">
         <f>IF(B32=0,0,B32/$B$33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="56">
+      <c r="B33" s="42">
         <f>SUM(B29:B32)</f>
         <v>7</v>
       </c>
-      <c r="C33" s="54"/>
+      <c r="C33" s="40"/>
     </row>
     <row r="35" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="49" t="s">
+      <c r="A35" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="B35" s="49"/>
-      <c r="C35" s="49"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
     </row>
     <row r="36" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="49" t="s">
+      <c r="A36" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="50" t="s">
+      <c r="B36" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="51" t="s">
+      <c r="C36" s="37" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="52" t="s">
+      <c r="A37" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="53">
+      <c r="B37" s="39">
         <v>0</v>
       </c>
-      <c r="C37" s="54">
+      <c r="C37" s="40">
         <f>IF(B37=0,0,B37/$B$33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="52" t="s">
+      <c r="A38" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="53">
+      <c r="B38" s="39">
         <v>0</v>
       </c>
-      <c r="C38" s="54">
+      <c r="C38" s="40">
         <f>IF(B38=0,0,B38/$B$33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="52" t="s">
+      <c r="A39" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="B39" s="53">
+      <c r="B39" s="39">
         <v>0</v>
       </c>
-      <c r="C39" s="54">
+      <c r="C39" s="40">
         <f>IF(B39=0,0,B39/$B$33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="52" t="s">
+      <c r="A40" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="B40" s="53">
+      <c r="B40" s="39">
         <v>0</v>
       </c>
-      <c r="C40" s="54">
+      <c r="C40" s="40">
         <f>IF(B40=0,0,B40/$B$33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="52" t="s">
+      <c r="A41" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="B41" s="53">
+      <c r="B41" s="39">
         <v>0</v>
       </c>
-      <c r="C41" s="54">
+      <c r="C41" s="40">
         <f>IF(B41=0,0,B41/$B$33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="55" t="s">
+      <c r="A42" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="56">
+      <c r="B42" s="42">
         <f>SUM(B37:B41)</f>
         <v>0</v>
       </c>
-      <c r="C42" s="54"/>
+      <c r="C42" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -7530,144 +7339,144 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="18" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="33">
+      <c r="A2" s="19">
         <v>46093</v>
       </c>
-      <c r="B2" s="33">
+      <c r="B2" s="19">
         <v>46094</v>
       </c>
-      <c r="C2" s="34">
+      <c r="C2" s="20">
         <f>D2/NETWORKDAYS(A2,B2)</f>
         <v>3.5</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="21">
         <f>'Status Report'!C7</f>
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="38" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="26" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="44">
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="30">
         <f>D2</f>
         <v>7</v>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="31">
         <f>D5</f>
         <v>7</v>
       </c>
-      <c r="F5" s="46">
+      <c r="F5" s="32">
         <v>0</v>
       </c>
-      <c r="G5" s="47" t="s">
+      <c r="G5" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="48">
+      <c r="H5" s="34">
         <f>D2</f>
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="41">
+      <c r="A6" s="27">
         <f>A2</f>
         <v>46093</v>
       </c>
-      <c r="B6" s="42">
+      <c r="B6" s="28">
         <f>IFERROR(WEEKDAY(A6,1),0)</f>
         <v>5</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="29">
         <f>IFERROR(WEEKDAY(B6,1),0)</f>
         <v>5</v>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="30">
         <f>D5-F6</f>
         <v>4</v>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="31">
         <f>D6</f>
         <v>4</v>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="32">
         <v>3</v>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="33">
         <v>7</v>
       </c>
-      <c r="H6" s="48">
+      <c r="H6" s="34">
         <f>IF(G6="","",H5-G6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="41">
+      <c r="A7" s="27">
         <f>WORKDAY(A6,1)</f>
         <v>46094</v>
       </c>
-      <c r="B7" s="42">
+      <c r="B7" s="28">
         <f>IFERROR(WEEKDAY(A7,1),0)</f>
         <v>6</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="29">
         <f>IFERROR(WEEKDAY(B7,1),0)</f>
         <v>6</v>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="30">
         <f>D6-F7</f>
         <v>0</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="31">
         <f>D7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="32">
         <v>4</v>
       </c>
-      <c r="G7" s="47">
+      <c r="G7" s="33">
         <f>COUNTIF([1]Scripts!F:F,A7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="48">
-        <f t="shared" ref="H6:H8" si="0">IF(G7="","",H6-G7)</f>
+      <c r="H7" s="34">
+        <f t="shared" ref="H7" si="0">IF(G7="","",H6-G7)</f>
         <v>0</v>
       </c>
     </row>
